--- a/inputan.xlsx
+++ b/inputan.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10125"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Personal\Katalon Studio\Sisfo Bahasa Remake\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/agungtrisnaa/Katalon Studio/Sisfo-Bahasa-Remake/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3079DBA1-6B1C-48F2-8159-083031BC25F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FD82207-7421-A14D-B69A-3FBF43905F63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-24525" yWindow="3735" windowWidth="21600" windowHeight="11295" xr2:uid="{B515BAB2-BCAD-4B7E-AD5C-E3DAB4375D2E}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="19660" xr2:uid="{B515BAB2-BCAD-4B7E-AD5C-E3DAB4375D2E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
   <si>
     <t>Link</t>
   </si>
@@ -139,6 +139,9 @@
   </si>
   <si>
     <t>IDsiswa</t>
+  </si>
+  <si>
+    <t>nSertif</t>
   </si>
 </sst>
 </file>
@@ -516,31 +519,32 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5B4298E-1260-483C-BDCD-A0BAF6E7D4E6}">
-  <dimension ref="A1:V8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:W8"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="35.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.28515625" customWidth="1"/>
-    <col min="5" max="5" width="19.5703125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="15.5703125" customWidth="1"/>
-    <col min="7" max="7" width="15.85546875" customWidth="1"/>
-    <col min="8" max="8" width="16.28515625" customWidth="1"/>
+    <col min="1" max="1" width="35.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.33203125" customWidth="1"/>
+    <col min="5" max="5" width="19.5" style="1" customWidth="1"/>
+    <col min="6" max="6" width="15.5" customWidth="1"/>
+    <col min="7" max="7" width="15.83203125" customWidth="1"/>
+    <col min="8" max="8" width="16.33203125" customWidth="1"/>
     <col min="9" max="9" width="13" customWidth="1"/>
-    <col min="10" max="10" width="12.7109375" customWidth="1"/>
-    <col min="11" max="11" width="18.28515625" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" customWidth="1"/>
-    <col min="13" max="13" width="12.28515625" customWidth="1"/>
-    <col min="14" max="14" width="12.140625" customWidth="1"/>
-    <col min="16" max="16" width="14.5703125" customWidth="1"/>
-    <col min="17" max="17" width="19.7109375" customWidth="1"/>
-    <col min="18" max="18" width="15.28515625" customWidth="1"/>
-    <col min="19" max="19" width="25.42578125" customWidth="1"/>
-    <col min="22" max="22" width="11.28515625" customWidth="1"/>
+    <col min="10" max="10" width="12.6640625" customWidth="1"/>
+    <col min="11" max="11" width="18.33203125" customWidth="1"/>
+    <col min="12" max="12" width="14.5" customWidth="1"/>
+    <col min="13" max="13" width="12.33203125" customWidth="1"/>
+    <col min="14" max="14" width="12.1640625" customWidth="1"/>
+    <col min="16" max="16" width="14.5" customWidth="1"/>
+    <col min="17" max="17" width="19.6640625" customWidth="1"/>
+    <col min="18" max="18" width="15.33203125" customWidth="1"/>
+    <col min="19" max="19" width="25.5" customWidth="1"/>
+    <col min="22" max="22" width="11.33203125" customWidth="1"/>
+    <col min="23" max="23" width="12.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:23" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -607,8 +611,11 @@
       <c r="V1" t="s">
         <v>37</v>
       </c>
+      <c r="W1" t="s">
+        <v>38</v>
+      </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -675,8 +682,11 @@
       <c r="V2">
         <v>1205497852</v>
       </c>
+      <c r="W2">
+        <v>17343643723</v>
+      </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D8" s="3"/>
     </row>
   </sheetData>

--- a/inputan.xlsx
+++ b/inputan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/agungtrisnaa/Katalon Studio/Sisfo-Bahasa-Remake/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FD82207-7421-A14D-B69A-3FBF43905F63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4552C691-6092-4745-A09F-DA5C352ECE78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="19660" xr2:uid="{B515BAB2-BCAD-4B7E-AD5C-E3DAB4375D2E}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
   <si>
     <t>Link</t>
   </si>
@@ -142,6 +142,15 @@
   </si>
   <si>
     <t>nSertif</t>
+  </si>
+  <si>
+    <t>nPeng</t>
+  </si>
+  <si>
+    <t>Penghargaan</t>
+  </si>
+  <si>
+    <t>Juara 1 Sholat</t>
   </si>
 </sst>
 </file>
@@ -223,9 +232,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -263,7 +272,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -369,7 +378,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -511,7 +520,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -519,7 +528,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5B4298E-1260-483C-BDCD-A0BAF6E7D4E6}">
-  <dimension ref="A1:W8"/>
+  <dimension ref="A1:Y8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="35.5" bestFit="1" customWidth="1"/>
@@ -542,9 +551,10 @@
     <col min="19" max="19" width="25.5" customWidth="1"/>
     <col min="22" max="22" width="11.33203125" customWidth="1"/>
     <col min="23" max="23" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="11.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -614,8 +624,14 @@
       <c r="W1" t="s">
         <v>38</v>
       </c>
+      <c r="X1" t="s">
+        <v>39</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>40</v>
+      </c>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -685,8 +701,14 @@
       <c r="W2">
         <v>17343643723</v>
       </c>
+      <c r="X2">
+        <v>1734834734</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>41</v>
+      </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D8" s="3"/>
     </row>
   </sheetData>

--- a/inputan.xlsx
+++ b/inputan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/agungtrisnaa/Katalon Studio/Sisfo-Bahasa-Remake/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4552C691-6092-4745-A09F-DA5C352ECE78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6271DBC-2D37-644A-BEE6-7F729494467B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="19660" xr2:uid="{B515BAB2-BCAD-4B7E-AD5C-E3DAB4375D2E}"/>
   </bookViews>
@@ -39,9 +39,6 @@
     <t>superadmin</t>
   </si>
   <si>
-    <t>Badiklat2025!</t>
-  </si>
-  <si>
     <t>fromDate</t>
   </si>
   <si>
@@ -151,6 +148,9 @@
   </si>
   <si>
     <t>Juara 1 Sholat</t>
+  </si>
+  <si>
+    <t>rahasia</t>
   </si>
 </sst>
 </file>
@@ -565,81 +565,81 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" t="s">
         <v>6</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>7</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>8</v>
       </c>
-      <c r="H1" t="s">
-        <v>9</v>
-      </c>
       <c r="I1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1" t="s">
         <v>11</v>
       </c>
-      <c r="J1" t="s">
-        <v>12</v>
-      </c>
       <c r="K1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="O1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P1" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="Q1" s="6" t="s">
+      <c r="R1" t="s">
         <v>29</v>
       </c>
-      <c r="R1" t="s">
-        <v>30</v>
-      </c>
       <c r="S1" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="T1" t="s">
+        <v>34</v>
+      </c>
+      <c r="U1" t="s">
         <v>35</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>36</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>37</v>
       </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
         <v>38</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
         <v>39</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="D2" s="2">
         <v>27040020261010</v>
@@ -648,43 +648,43 @@
         <v>28040020261010</v>
       </c>
       <c r="F2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" t="s">
         <v>13</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>14</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>15</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>16</v>
       </c>
-      <c r="J2" t="s">
-        <v>17</v>
-      </c>
       <c r="K2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="O2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P2" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q2" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="Q2" s="5" t="s">
-        <v>34</v>
-      </c>
       <c r="R2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="S2">
         <v>5354242343</v>
@@ -705,7 +705,7 @@
         <v>1734834734</v>
       </c>
       <c r="Y2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.2">

--- a/inputan.xlsx
+++ b/inputan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/agungtrisnaa/Katalon Studio/Sisfo-Bahasa-Remake/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6271DBC-2D37-644A-BEE6-7F729494467B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFD53EC8-147B-674A-B076-1669203AE02E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="19660" xr2:uid="{B515BAB2-BCAD-4B7E-AD5C-E3DAB4375D2E}"/>
   </bookViews>
@@ -150,7 +150,7 @@
     <t>Juara 1 Sholat</t>
   </si>
   <si>
-    <t>rahasia</t>
+    <t>Badiklat2025!</t>
   </si>
 </sst>
 </file>

--- a/inputan.xlsx
+++ b/inputan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/agungtrisnaa/Katalon Studio/Sisfo-Bahasa-Remake/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFD53EC8-147B-674A-B076-1669203AE02E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD6A7F2F-235C-6640-ABBC-006CCD78B2DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="19660" xr2:uid="{B515BAB2-BCAD-4B7E-AD5C-E3DAB4375D2E}"/>
   </bookViews>
@@ -150,7 +150,7 @@
     <t>Juara 1 Sholat</t>
   </si>
   <si>
-    <t>Badiklat2025!</t>
+    <t>rahasia</t>
   </si>
 </sst>
 </file>

--- a/inputan.xlsx
+++ b/inputan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/agungtrisnaa/Katalon Studio/Sisfo-Bahasa-Remake/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD6A7F2F-235C-6640-ABBC-006CCD78B2DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{737F7ABA-24E9-624D-9FA2-8DC2BFF03017}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="19660" xr2:uid="{B515BAB2-BCAD-4B7E-AD5C-E3DAB4375D2E}"/>
   </bookViews>
@@ -150,7 +150,7 @@
     <t>Juara 1 Sholat</t>
   </si>
   <si>
-    <t>rahasia</t>
+    <t>Badiklat2025!</t>
   </si>
 </sst>
 </file>

--- a/inputan.xlsx
+++ b/inputan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/agungtrisnaa/Katalon Studio/Sisfo-Bahasa-Remake/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{737F7ABA-24E9-624D-9FA2-8DC2BFF03017}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D248FA7-6542-F045-84F9-ADE126029371}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="19660" xr2:uid="{B515BAB2-BCAD-4B7E-AD5C-E3DAB4375D2E}"/>
   </bookViews>
@@ -150,7 +150,7 @@
     <t>Juara 1 Sholat</t>
   </si>
   <si>
-    <t>Badiklat2025!</t>
+    <t>rahasia</t>
   </si>
 </sst>
 </file>

--- a/inputan.xlsx
+++ b/inputan.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10125"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/agungtrisnaa/Katalon Studio/Sisfo-Bahasa-Remake/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Personal\Katalon Studio\Sisfo Bahasa Remake\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D248FA7-6542-F045-84F9-ADE126029371}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5A587F9-6A1A-40EA-BBAD-984FD6DD5AE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="19660" xr2:uid="{B515BAB2-BCAD-4B7E-AD5C-E3DAB4375D2E}"/>
+    <workbookView xWindow="-24525" yWindow="3735" windowWidth="21600" windowHeight="11295" xr2:uid="{B515BAB2-BCAD-4B7E-AD5C-E3DAB4375D2E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -150,7 +150,7 @@
     <t>Juara 1 Sholat</t>
   </si>
   <si>
-    <t>rahasia</t>
+    <t>Badiklat2025!</t>
   </si>
 </sst>
 </file>
@@ -232,9 +232,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -272,7 +272,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -378,7 +378,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -520,7 +520,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -529,32 +529,32 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5B4298E-1260-483C-BDCD-A0BAF6E7D4E6}">
   <dimension ref="A1:Y8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="35.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.83203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.33203125" customWidth="1"/>
-    <col min="5" max="5" width="19.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="15.5" customWidth="1"/>
-    <col min="7" max="7" width="15.83203125" customWidth="1"/>
-    <col min="8" max="8" width="16.33203125" customWidth="1"/>
+    <col min="1" max="1" width="35.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.28515625" customWidth="1"/>
+    <col min="5" max="5" width="19.42578125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="15.42578125" customWidth="1"/>
+    <col min="7" max="7" width="15.85546875" customWidth="1"/>
+    <col min="8" max="8" width="16.28515625" customWidth="1"/>
     <col min="9" max="9" width="13" customWidth="1"/>
-    <col min="10" max="10" width="12.6640625" customWidth="1"/>
-    <col min="11" max="11" width="18.33203125" customWidth="1"/>
-    <col min="12" max="12" width="14.5" customWidth="1"/>
-    <col min="13" max="13" width="12.33203125" customWidth="1"/>
-    <col min="14" max="14" width="12.1640625" customWidth="1"/>
-    <col min="16" max="16" width="14.5" customWidth="1"/>
-    <col min="17" max="17" width="19.6640625" customWidth="1"/>
-    <col min="18" max="18" width="15.33203125" customWidth="1"/>
-    <col min="19" max="19" width="25.5" customWidth="1"/>
-    <col min="22" max="22" width="11.33203125" customWidth="1"/>
-    <col min="23" max="23" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.7109375" customWidth="1"/>
+    <col min="11" max="11" width="18.28515625" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" customWidth="1"/>
+    <col min="13" max="13" width="12.28515625" customWidth="1"/>
+    <col min="14" max="14" width="12.140625" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" customWidth="1"/>
+    <col min="17" max="17" width="19.7109375" customWidth="1"/>
+    <col min="18" max="18" width="15.28515625" customWidth="1"/>
+    <col min="19" max="19" width="25.42578125" customWidth="1"/>
+    <col min="22" max="22" width="11.28515625" customWidth="1"/>
+    <col min="23" max="23" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="11.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -631,7 +631,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -708,7 +708,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
       <c r="D8" s="3"/>
     </row>
   </sheetData>

--- a/inputan.xlsx
+++ b/inputan.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Personal\Katalon Studio\Sisfo Bahasa Remake\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5A587F9-6A1A-40EA-BBAD-984FD6DD5AE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1D4FEB3-7DF4-45F6-90FF-1481A640FE5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-24525" yWindow="3735" windowWidth="21600" windowHeight="11295" xr2:uid="{B515BAB2-BCAD-4B7E-AD5C-E3DAB4375D2E}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B515BAB2-BCAD-4B7E-AD5C-E3DAB4375D2E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -150,7 +150,7 @@
     <t>Juara 1 Sholat</t>
   </si>
   <si>
-    <t>Badiklat2025!</t>
+    <t>rahasia</t>
   </si>
 </sst>
 </file>

--- a/inputan.xlsx
+++ b/inputan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Personal\Katalon Studio\Sisfo Bahasa Remake\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1D4FEB3-7DF4-45F6-90FF-1481A640FE5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10BD61AC-A99E-4F17-9098-7A13343B8863}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B515BAB2-BCAD-4B7E-AD5C-E3DAB4375D2E}"/>
   </bookViews>
